--- a/public/downloads/ZhaoImproved2019.xlsx
+++ b/public/downloads/ZhaoImproved2019.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>HO2</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
+  </si>
+  <si>
+    <t>HO2</t>
   </si>
   <si>
     <t>O</t>
@@ -659,10 +682,10 @@
         <v>30</v>
       </c>
       <c r="N3" s="5">
-        <v>7466.915946245193</v>
+        <v>7466915.946245193</v>
       </c>
       <c r="O3" s="4">
-        <v>0.1264657274570261</v>
+        <v>126.4657274570261</v>
       </c>
       <c r="P3" s="5">
         <v>59043</v>
@@ -709,10 +732,10 @@
         <v>30</v>
       </c>
       <c r="N4" s="5">
-        <v>1317.070265769958</v>
+        <v>1317070.265769958</v>
       </c>
       <c r="O4" s="4">
-        <v>0.1195163580553501</v>
+        <v>119.5163580553501</v>
       </c>
       <c r="P4" s="5">
         <v>11020</v>
@@ -759,10 +782,10 @@
         <v>30</v>
       </c>
       <c r="N5" s="5">
-        <v>4136.306657314301</v>
+        <v>4136306.657314301</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1349749276330331</v>
+        <v>134.9749276330332</v>
       </c>
       <c r="P5" s="5">
         <v>30645</v>
@@ -809,10 +832,10 @@
         <v>30</v>
       </c>
       <c r="N6" s="5">
-        <v>2233.406391143799</v>
+        <v>2233406.391143799</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1139318671195123</v>
+        <v>113.9318671195122</v>
       </c>
       <c r="P6" s="5">
         <v>19603</v>
@@ -859,10 +882,10 @@
         <v>30</v>
       </c>
       <c r="N7" s="5">
-        <v>1446.419043779373</v>
+        <v>1446419.043779373</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1794341947375478</v>
+        <v>179.4341947375478</v>
       </c>
       <c r="P7" s="5">
         <v>8061</v>
@@ -909,10 +932,10 @@
         <v>30</v>
       </c>
       <c r="N8" s="5">
-        <v>919.9851145744324</v>
+        <v>919985.1145744324</v>
       </c>
       <c r="O8" s="4">
-        <v>0.05970052657848361</v>
+        <v>59.7005265784836</v>
       </c>
       <c r="P8" s="5">
         <v>15410</v>
@@ -959,10 +982,10 @@
         <v>30</v>
       </c>
       <c r="N9" s="5">
-        <v>1030.383352279663</v>
+        <v>1030383.352279663</v>
       </c>
       <c r="O9" s="4">
-        <v>0.06018594347427939</v>
+        <v>60.18594347427938</v>
       </c>
       <c r="P9" s="5">
         <v>17120</v>
@@ -1009,10 +1032,10 @@
         <v>30</v>
       </c>
       <c r="N10" s="5">
-        <v>889.47962474823</v>
+        <v>889479.62474823</v>
       </c>
       <c r="O10" s="4">
-        <v>0.1108523959058113</v>
+        <v>110.8523959058113</v>
       </c>
       <c r="P10" s="5">
         <v>8024</v>
@@ -1059,10 +1082,10 @@
         <v>30</v>
       </c>
       <c r="N11" s="5">
-        <v>1210.477239131927</v>
+        <v>1210477.239131927</v>
       </c>
       <c r="O11" s="4">
-        <v>0.06170237736425362</v>
+        <v>61.70237736425361</v>
       </c>
       <c r="P11" s="5">
         <v>19618</v>
@@ -1109,10 +1132,10 @@
         <v>30</v>
       </c>
       <c r="N12" s="5">
-        <v>778.1776609420776</v>
+        <v>778177.6609420776</v>
       </c>
       <c r="O12" s="4">
-        <v>0.05265428384478501</v>
+        <v>52.65428384478501</v>
       </c>
       <c r="P12" s="5">
         <v>14779</v>
@@ -1159,10 +1182,10 @@
         <v>30</v>
       </c>
       <c r="N13" s="5">
-        <v>1768.138210296631</v>
+        <v>1768138.210296631</v>
       </c>
       <c r="O13" s="4">
-        <v>0.09337936151553371</v>
+        <v>93.3793615155337</v>
       </c>
       <c r="P13" s="5">
         <v>18935</v>
@@ -1209,10 +1232,10 @@
         <v>30</v>
       </c>
       <c r="N14" s="5">
-        <v>2250.458378553391</v>
+        <v>2250458.378553391</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2266779188712118</v>
+        <v>226.6779188712118</v>
       </c>
       <c r="P14" s="5">
         <v>9928</v>
@@ -1259,10 +1282,10 @@
         <v>30</v>
       </c>
       <c r="N15" s="5">
-        <v>1994.258942365646</v>
+        <v>1994258.942365646</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2020730512073813</v>
+        <v>202.0730512073813</v>
       </c>
       <c r="P15" s="5">
         <v>9869</v>
@@ -1309,10 +1332,10 @@
         <v>30</v>
       </c>
       <c r="N16" s="5">
-        <v>1159.972180604935</v>
+        <v>1159972.180604935</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1060594478014935</v>
+        <v>106.0594478014935</v>
       </c>
       <c r="P16" s="5">
         <v>10937</v>
@@ -1359,10 +1382,10 @@
         <v>30</v>
       </c>
       <c r="N17" s="5">
-        <v>1761.323483705521</v>
+        <v>1761323.483705521</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1051976039960294</v>
+        <v>105.1976039960294</v>
       </c>
       <c r="P17" s="5">
         <v>16743</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,198 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5578929446367672</v>
+        <v>1.431127466988059</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3973123906040492</v>
+        <v>1.15571395946091</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2317909146294575</v>
+        <v>0.9744743876134768</v>
       </c>
       <c r="E3" s="4">
-        <v>69.78571428571429</v>
+        <v>37.89795918367347</v>
       </c>
       <c r="F3" s="4">
-        <v>66.15100671140939</v>
+        <v>42.96644295302013</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.431127466988059</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.15571395946091</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2334673235106972</v>
+        <v>1.136651778138612</v>
       </c>
       <c r="C4" s="4">
-        <v>0.153022585989443</v>
+        <v>1.428706260045295</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1579536764614618</v>
+        <v>1.384502860059946</v>
       </c>
       <c r="E4" s="4">
-        <v>74.77891156462584</v>
+        <v>33.79591836734694</v>
       </c>
       <c r="F4" s="4">
-        <v>71.35682326621921</v>
+        <v>33.76510067114094</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
         <v>7</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.136651778138612</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.428706260045295</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6051484095189458</v>
+        <v>1.07398340108341</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1192016913121516</v>
+        <v>1.516096138072527</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1828717066585614</v>
+        <v>0.9721605009441336</v>
       </c>
       <c r="E5" s="4">
-        <v>68.8503401360544</v>
+        <v>33.62244897959184</v>
       </c>
       <c r="F5" s="4">
-        <v>67.33557046979865</v>
+        <v>39.13422818791946</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
       <c r="H5" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
+        <v>7</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>3</v>
       </c>
-      <c r="M5" s="5">
-        <v>0</v>
+      <c r="P5" s="4">
+        <v>1.07398340108341</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.516096138072527</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1699,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1718,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1760,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,107 +1791,157 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.492387290375007</v>
+        <v>0.44593740967847</v>
       </c>
       <c r="C3" s="4">
-        <v>0.03922750697510935</v>
+        <v>0.1268916547332708</v>
       </c>
       <c r="D3" s="4">
-        <v>1.215104088571775</v>
+        <v>0.4733729682949047</v>
       </c>
       <c r="E3" s="4">
-        <v>36.12925170068026</v>
+        <v>31.15646258503401</v>
       </c>
       <c r="F3" s="4">
-        <v>39.17114093959724</v>
+        <v>37.10850111856831</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
         <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>7</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.44593740967847</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1268916547332708</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6740145516381858</v>
+        <v>0.8368043941586848</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1403749448827938</v>
+        <v>0.8235127788458101</v>
       </c>
       <c r="D4" s="4">
-        <v>0.9801231475168436</v>
+        <v>0.9718017620175715</v>
       </c>
       <c r="E4" s="4">
-        <v>39.59523809523822</v>
+        <v>32.18367346938775</v>
       </c>
       <c r="F4" s="4">
-        <v>45.11185682326633</v>
+        <v>38.64541387024607</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8368043941586848</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8235127788458101</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.002872625533203</v>
+        <v>1.225407485429676</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1683607124511326</v>
+        <v>0.7718361505773998</v>
       </c>
       <c r="D5" s="4">
-        <v>0.9676122138208001</v>
+        <v>0.8779370976000933</v>
       </c>
       <c r="E5" s="4">
-        <v>45.20068027210885</v>
+        <v>34.23809523809511</v>
       </c>
       <c r="F5" s="4">
-        <v>47.92170022371367</v>
+        <v>41.08948545861255</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -1788,17 +1956,33 @@
         <v>8</v>
       </c>
       <c r="K5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.225407485429676</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7718361505773998</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +1993,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2001,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2012,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2054,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2085,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6060789637631785</v>
+        <v>0.2334673235106972</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3166853809855089</v>
+        <v>0.153022585989443</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7024976091328086</v>
+        <v>0.1579536764614618</v>
       </c>
       <c r="E3" s="4">
-        <v>53.92517006802745</v>
+        <v>74.77891156462584</v>
       </c>
       <c r="F3" s="4">
-        <v>55.38366890380318</v>
+        <v>71.35682326621921</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>3</v>
       </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.04838457539003503</v>
+      </c>
+      <c r="O3" s="5">
         <v>7</v>
       </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>5</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="P3" s="4">
+        <v>0.2371043843460234</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1513063049841898</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.742752890264643</v>
+        <v>0.5578929446367672</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.3973123906040492</v>
       </c>
       <c r="D4" s="4">
-        <v>0.548994963818825</v>
+        <v>0.2317909146294575</v>
       </c>
       <c r="E4" s="4">
-        <v>50.15646258503409</v>
+        <v>69.78571428571429</v>
       </c>
       <c r="F4" s="4">
-        <v>52.10402684563797</v>
+        <v>66.15100671140939</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.148383240401354</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5738148273977693</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4842293499061472</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8201325865424707</v>
+        <v>0.6051484095189458</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2800941658943354</v>
+        <v>0.1192016913121516</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6093438385917949</v>
+        <v>0.1828717066585614</v>
       </c>
       <c r="E5" s="4">
-        <v>50.12585034013605</v>
+        <v>68.8503401360544</v>
       </c>
       <c r="F5" s="4">
-        <v>53.25167785234909</v>
+        <v>67.33557046979865</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
       <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>4</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
         <v>3</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>7</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>5</v>
-      </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.03787092604290828</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6051484095189458</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1192016913121516</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2293,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2301,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2312,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2354,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,107 +2385,157 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>2.10915798804138</v>
+        <v>0.6740145516381858</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.1403749448827938</v>
       </c>
       <c r="D3" s="4">
-        <v>1.473262973480467</v>
+        <v>0.9801231475168436</v>
       </c>
       <c r="E3" s="4">
-        <v>32.88775510204081</v>
+        <v>39.59523809523822</v>
       </c>
       <c r="F3" s="4">
-        <v>32.4496644295302</v>
+        <v>45.11185682326633</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
         <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
         <v>2</v>
       </c>
-      <c r="L3" s="5">
-        <v>7</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="P3" s="4">
+        <v>0.6740145516381858</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1403749448827938</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8842005364765555</v>
+        <v>1.492387290375007</v>
       </c>
       <c r="C4" s="4">
-        <v>0.01066092049742906</v>
+        <v>0.03922750697510935</v>
       </c>
       <c r="D4" s="4">
-        <v>1.085716945214847</v>
+        <v>1.215104088571775</v>
       </c>
       <c r="E4" s="4">
-        <v>36.63265306122449</v>
+        <v>36.12925170068026</v>
       </c>
       <c r="F4" s="4">
-        <v>36.99440715883668</v>
+        <v>39.17114093959724</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.492387290375007</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03922750697510935</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>4.041110492219244</v>
+        <v>2.002872625533203</v>
       </c>
       <c r="C5" s="4">
-        <v>1.610598899080799</v>
+        <v>0.1683607124511326</v>
       </c>
       <c r="D5" s="4">
-        <v>1.033503616414069</v>
+        <v>0.9676122138208001</v>
       </c>
       <c r="E5" s="4">
-        <v>36.56122448979585</v>
+        <v>45.20068027210885</v>
       </c>
       <c r="F5" s="4">
-        <v>40.4507829977625</v>
+        <v>47.92170022371367</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -2214,17 +2550,33 @@
         <v>8</v>
       </c>
       <c r="K5" s="5">
+        <v>4</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.002872625533203</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1683607124511326</v>
+      </c>
+      <c r="R5" s="5">
         <v>2</v>
       </c>
-      <c r="L5" s="5">
-        <v>5</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="S5" s="5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2587,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2595,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2606,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2648,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,66 +2679,96 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7121792676611435</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.09576349016246333</v>
-      </c>
+        <v>0.742752890264643</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.668986414491728</v>
+        <v>0.548994963818825</v>
       </c>
       <c r="E3" s="4">
-        <v>43.67006802721087</v>
+        <v>50.15646258503409</v>
       </c>
       <c r="F3" s="4">
-        <v>44.94407158836719</v>
+        <v>52.10402684563797</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>10</v>
+      </c>
+      <c r="K3" s="5">
         <v>2</v>
       </c>
-      <c r="J3" s="5">
-        <v>7</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.742752890264643</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3621151538561085</v>
+        <v>0.6060789637631785</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3568980483581791</v>
+        <v>0.3166853809855089</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3155226976832254</v>
+        <v>0.7024976091328086</v>
       </c>
       <c r="E4" s="4">
-        <v>47.78571428571428</v>
+        <v>53.92517006802745</v>
       </c>
       <c r="F4" s="4">
-        <v>54.04697986577181</v>
+        <v>55.38366890380318</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -2386,58 +2783,90 @@
         <v>7</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6060789637631785</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3166853809855089</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7592712961413649</v>
+        <v>0.8201325865424707</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1863886997206243</v>
+        <v>0.2800941658943354</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3498314181184899</v>
+        <v>0.6093438385917949</v>
       </c>
       <c r="E5" s="4">
-        <v>47.52380952380953</v>
+        <v>50.12585034013605</v>
       </c>
       <c r="F5" s="4">
-        <v>54.04474272930645</v>
+        <v>53.25167785234909</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
       <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>7</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>4</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>6</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>6</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
+      <c r="P5" s="4">
+        <v>0.8201325865424707</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2800941658943354</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2877,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2885,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2896,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2938,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2969,194 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>6.855673812313412</v>
+        <v>0.8842005364765555</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6623312957213301</v>
+        <v>0.01066092049742906</v>
       </c>
       <c r="D3" s="4">
-        <v>6.195481036587188</v>
+        <v>1.085716945214847</v>
       </c>
       <c r="E3" s="4">
-        <v>58.13265306122457</v>
+        <v>36.63265306122449</v>
       </c>
       <c r="F3" s="4">
-        <v>61.58948545861369</v>
+        <v>36.99440715883668</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
         <v>8</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>6</v>
-      </c>
       <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8842005364765555</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.01066092049742906</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>3.145339368345299</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2519928086249503</v>
-      </c>
+        <v>2.10915798804138</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>2.718396572282765</v>
+        <v>1.473262973480467</v>
       </c>
       <c r="E4" s="4">
-        <v>55.53061224489796</v>
+        <v>32.88775510204081</v>
       </c>
       <c r="F4" s="4">
-        <v>56.42393736017966</v>
+        <v>32.4496644295302</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
+        <v>9</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
         <v>7</v>
       </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>6</v>
-      </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.10915798804138</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.888688393171385</v>
+        <v>4.041110492219244</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3437371515767236</v>
+        <v>1.610598899080799</v>
       </c>
       <c r="D5" s="4">
-        <v>2.868623514707692</v>
+        <v>1.033503616414069</v>
       </c>
       <c r="E5" s="4">
-        <v>50.74829931972789</v>
+        <v>36.56122448979585</v>
       </c>
       <c r="F5" s="4">
-        <v>55.910514541387</v>
+        <v>40.4507829977625</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
         <v>5</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>4.041110492219244</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.610598899080799</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3167,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3175,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3186,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3228,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3259,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5689757133247102</v>
+        <v>0.3621151538561085</v>
       </c>
       <c r="C3" s="4">
-        <v>0.550260672052417</v>
+        <v>0.3568980483581791</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6077064411038592</v>
+        <v>0.3155226976832254</v>
       </c>
       <c r="E3" s="4">
-        <v>45.07142857142859</v>
+        <v>47.78571428571428</v>
       </c>
       <c r="F3" s="4">
-        <v>51.20917225950799</v>
+        <v>54.04697986577181</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
@@ -2765,48 +3304,64 @@
         <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3621151538561085</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3568980483581791</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2804485875835993</v>
+        <v>0.7121792676611435</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3245488493015632</v>
+        <v>0.09576349016246333</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2971288503368257</v>
+        <v>0.668986414491728</v>
       </c>
       <c r="E4" s="4">
-        <v>48.10544217687075</v>
+        <v>43.67006802721087</v>
       </c>
       <c r="F4" s="4">
-        <v>55.14653243847872</v>
+        <v>44.94407158836719</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>7</v>
@@ -2820,25 +3375,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7121792676611435</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09576349016246333</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6561404936292272</v>
+        <v>0.7592712961413649</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1658954158527883</v>
+        <v>0.1863886997206243</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3235658982610237</v>
+        <v>0.3498314181184899</v>
       </c>
       <c r="E5" s="4">
-        <v>47.71768707482993</v>
+        <v>47.52380952380953</v>
       </c>
       <c r="F5" s="4">
-        <v>53.46756152125278</v>
+        <v>54.04474272930645</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -2861,9 +3432,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7592712961413649</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1863886997206243</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3461,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3469,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3480,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3522,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,78 +3553,112 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>2.010195920368608</v>
+        <v>3.145339368345299</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8624621790323346</v>
+        <v>0.2519928086249503</v>
       </c>
       <c r="D3" s="4">
-        <v>2.93855236636219</v>
+        <v>2.718396572282765</v>
       </c>
       <c r="E3" s="4">
-        <v>54.82993197278912</v>
+        <v>55.53061224489796</v>
       </c>
       <c r="F3" s="4">
-        <v>57.91387024608501</v>
+        <v>56.42393736017966</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
         <v>4</v>
       </c>
-      <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="P3" s="4">
+        <v>3.145339368345299</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2519928086249503</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4925827407410772</v>
+        <v>6.855673812313412</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2514190901120719</v>
+        <v>0.6623312957213301</v>
       </c>
       <c r="D4" s="4">
-        <v>1.570721759114359</v>
+        <v>6.195481036587188</v>
       </c>
       <c r="E4" s="4">
-        <v>51.88095238095239</v>
+        <v>58.13265306122457</v>
       </c>
       <c r="F4" s="4">
-        <v>54.87807606263982</v>
+        <v>61.58948545861369</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -3031,27 +3667,43 @@
         <v>6</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>6.855673812313412</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6623312957213301</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7596902437805746</v>
+        <v>2.888688393171385</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4511796191550204</v>
+        <v>0.3437371515767236</v>
       </c>
       <c r="D5" s="4">
-        <v>1.617823508477746</v>
+        <v>2.868623514707692</v>
       </c>
       <c r="E5" s="4">
-        <v>55.0544217687075</v>
+        <v>50.74829931972789</v>
       </c>
       <c r="F5" s="4">
-        <v>57.1230425055922</v>
+        <v>55.910514541387</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -3074,9 +3726,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.888688393171385</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3437371515767236</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3755,1458 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2804485875835993</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3245488493015632</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2971288503368257</v>
+      </c>
+      <c r="E3" s="4">
+        <v>48.10544217687075</v>
+      </c>
+      <c r="F3" s="4">
+        <v>55.14653243847872</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>7</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>7</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2804485875835993</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3245488493015632</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5689757133247102</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.550260672052417</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6077064411038592</v>
+      </c>
+      <c r="E4" s="4">
+        <v>45.07142857142859</v>
+      </c>
+      <c r="F4" s="4">
+        <v>51.20917225950799</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5689757133247102</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.550260672052417</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6561404936292272</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1658954158527883</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3235658982610237</v>
+      </c>
+      <c r="E5" s="4">
+        <v>47.71768707482993</v>
+      </c>
+      <c r="F5" s="4">
+        <v>53.46756152125278</v>
+      </c>
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>6</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6561404936292272</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1658954158527883</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4925827407410772</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2514190901120719</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.570721759114359</v>
+      </c>
+      <c r="E3" s="4">
+        <v>51.88095238095239</v>
+      </c>
+      <c r="F3" s="4">
+        <v>54.87807606263982</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4925827407410772</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2514190901120719</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2.010195920368608</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.8624621790323346</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2.93855236636219</v>
+      </c>
+      <c r="E4" s="4">
+        <v>54.82993197278912</v>
+      </c>
+      <c r="F4" s="4">
+        <v>57.91387024608501</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.010195920368608</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8624621790323346</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.7596902437805746</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4511796191550204</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.617823508477746</v>
+      </c>
+      <c r="E5" s="4">
+        <v>55.0544217687075</v>
+      </c>
+      <c r="F5" s="4">
+        <v>57.1230425055922</v>
+      </c>
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>6</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7596902437805746</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4511796191550204</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="E3" s="3">
+        <v>36.66666666666666</v>
+      </c>
+      <c r="F3" s="3">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.210300482558299</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2204654167498177</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.9628557297252115</v>
+      </c>
+      <c r="K3" s="4">
+        <v>22.85714285714283</v>
+      </c>
+      <c r="L3" s="4">
+        <v>34.5768083519764</v>
+      </c>
+      <c r="M3" s="5">
+        <v>30</v>
+      </c>
+      <c r="N3" s="5">
+        <v>7466915.946245193</v>
+      </c>
+      <c r="O3" s="4">
+        <v>126.4657274570261</v>
+      </c>
+      <c r="P3" s="5">
+        <v>59043</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D4" s="3">
+        <v>80</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F4" s="3">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.019443532675756</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.7211483457321719</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.8682920468892358</v>
+      </c>
+      <c r="K4" s="4">
+        <v>39.90136054421781</v>
+      </c>
+      <c r="L4" s="4">
+        <v>50.99366144668124</v>
+      </c>
+      <c r="M4" s="5">
+        <v>30</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1317070.265769958</v>
+      </c>
+      <c r="O4" s="4">
+        <v>119.5163580553501</v>
+      </c>
+      <c r="P4" s="5">
+        <v>11020</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="E5" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="F5" s="3">
+        <v>60</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1.333613917932247</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2405207381436298</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.8366714396689863</v>
+      </c>
+      <c r="K5" s="4">
+        <v>30.78117913832202</v>
+      </c>
+      <c r="L5" s="4">
+        <v>39.18978374347493</v>
+      </c>
+      <c r="M5" s="5">
+        <v>30</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4136306.657314301</v>
+      </c>
+      <c r="O5" s="4">
+        <v>134.9749276330332</v>
+      </c>
+      <c r="P5" s="5">
+        <v>30645</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D6" s="3">
+        <v>80</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F6" s="3">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1.134768158858716</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3306888379185693</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.6132153452288274</v>
+      </c>
+      <c r="K6" s="4">
+        <v>24.49206349206348</v>
+      </c>
+      <c r="L6" s="4">
+        <v>31.63609246830675</v>
+      </c>
+      <c r="M6" s="5">
+        <v>30</v>
+      </c>
+      <c r="N6" s="5">
+        <v>2233406.391143799</v>
+      </c>
+      <c r="O6" s="4">
+        <v>113.9318671195122</v>
+      </c>
+      <c r="P6" s="5">
+        <v>19603</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>36.66666666666666</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D7" s="3">
+        <v>60</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>60</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.7295268617338352</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.854338263861921</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.7157839879399226</v>
+      </c>
+      <c r="K7" s="4">
+        <v>57.17460317460286</v>
+      </c>
+      <c r="L7" s="4">
+        <v>60.33780760626353</v>
+      </c>
+      <c r="M7" s="5">
+        <v>30</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1446419.043779373</v>
+      </c>
+      <c r="O7" s="4">
+        <v>179.4341947375478</v>
+      </c>
+      <c r="P7" s="5">
+        <v>8061</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D8" s="3">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>70</v>
+      </c>
+      <c r="G8" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1.213920882070027</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1.366838785859577</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1.110379249539185</v>
+      </c>
+      <c r="K8" s="4">
+        <v>35.10544217687077</v>
+      </c>
+      <c r="L8" s="4">
+        <v>38.6219239373596</v>
+      </c>
+      <c r="M8" s="5">
+        <v>30</v>
+      </c>
+      <c r="N8" s="5">
+        <v>919985.1145744324</v>
+      </c>
+      <c r="O8" s="4">
+        <v>59.7005265784836</v>
+      </c>
+      <c r="P8" s="5">
+        <v>15410</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="C9" s="3">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="F9" s="3">
+        <v>70</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.8360497630889436</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.6235191836834701</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.7743706093041899</v>
+      </c>
+      <c r="K9" s="4">
+        <v>32.52607709750556</v>
+      </c>
+      <c r="L9" s="4">
+        <v>38.94780014914289</v>
+      </c>
+      <c r="M9" s="5">
+        <v>30</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1030383.352279663</v>
+      </c>
+      <c r="O9" s="4">
+        <v>60.18594347427938</v>
+      </c>
+      <c r="P9" s="5">
+        <v>17120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>60</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D10" s="3">
+        <v>36.66666666666666</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F10" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.4720225404209129</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.233083390682943</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2142124607509016</v>
+      </c>
+      <c r="K10" s="4">
+        <v>71.13832199546474</v>
+      </c>
+      <c r="L10" s="4">
+        <v>68.28113348247568</v>
+      </c>
+      <c r="M10" s="5">
+        <v>30</v>
+      </c>
+      <c r="N10" s="5">
+        <v>889479.62474823</v>
+      </c>
+      <c r="O10" s="4">
+        <v>110.8523959058113</v>
+      </c>
+      <c r="P10" s="5">
+        <v>8024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D11" s="3">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="E11" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="F11" s="3">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1.389758155848799</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1159877214363452</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1.054279816636473</v>
+      </c>
+      <c r="K11" s="4">
+        <v>40.30839002267583</v>
+      </c>
+      <c r="L11" s="4">
+        <v>44.068232662192</v>
+      </c>
+      <c r="M11" s="5">
+        <v>30</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1210477.239131927</v>
+      </c>
+      <c r="O11" s="4">
+        <v>61.70237736425361</v>
+      </c>
+      <c r="P11" s="5">
+        <v>19618</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>80</v>
+      </c>
+      <c r="E12" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="F12" s="3">
+        <v>60</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.722988146856764</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2983897734399221</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.6202788038478094</v>
+      </c>
+      <c r="K12" s="4">
+        <v>51.40249433106597</v>
+      </c>
+      <c r="L12" s="4">
+        <v>53.57979120059647</v>
+      </c>
+      <c r="M12" s="5">
+        <v>30</v>
+      </c>
+      <c r="N12" s="5">
+        <v>778177.6609420776</v>
+      </c>
+      <c r="O12" s="4">
+        <v>52.65428384478501</v>
+      </c>
+      <c r="P12" s="5">
+        <v>14779</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D13" s="3">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="E13" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="F13" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="G13" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="H13" s="4">
+        <v>2.34482300557906</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1.077286239553009</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1.197494511703128</v>
+      </c>
+      <c r="K13" s="4">
+        <v>35.3605442176872</v>
+      </c>
+      <c r="L13" s="4">
+        <v>36.63161819537625</v>
+      </c>
+      <c r="M13" s="5">
+        <v>30</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1768138.210296631</v>
+      </c>
+      <c r="O13" s="4">
+        <v>93.3793615155337</v>
+      </c>
+      <c r="P13" s="5">
+        <v>18935</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="C14" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D14" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.6111885725528724</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2390015542649372</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.4447801767644811</v>
+      </c>
+      <c r="K14" s="4">
+        <v>46.32653061224497</v>
+      </c>
+      <c r="L14" s="4">
+        <v>51.01193139448245</v>
+      </c>
+      <c r="M14" s="5">
+        <v>30</v>
+      </c>
+      <c r="N14" s="5">
+        <v>2250458.378553391</v>
+      </c>
+      <c r="O14" s="4">
+        <v>226.6779188712118</v>
+      </c>
+      <c r="P14" s="5">
+        <v>9928</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>30</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>70</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F15" s="3">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G15" s="3">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4">
+        <v>4.296567191276699</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.3839544026249339</v>
+      </c>
+      <c r="J15" s="4">
+        <v>3.927500374525882</v>
+      </c>
+      <c r="K15" s="4">
+        <v>54.80385487528344</v>
+      </c>
+      <c r="L15" s="4">
+        <v>57.9746457867266</v>
+      </c>
+      <c r="M15" s="5">
+        <v>30</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1994258.942365646</v>
+      </c>
+      <c r="O15" s="4">
+        <v>202.0730512073813</v>
+      </c>
+      <c r="P15" s="5">
+        <v>9869</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D16" s="3">
+        <v>63.33333333333333</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>63.33333333333333</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5018549315125124</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.3288010227473094</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.4094670632339028</v>
+      </c>
+      <c r="K16" s="4">
+        <v>46.96485260770974</v>
+      </c>
+      <c r="L16" s="4">
+        <v>53.27442207308005</v>
+      </c>
+      <c r="M16" s="5">
+        <v>30</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1159972.180604935</v>
+      </c>
+      <c r="O16" s="4">
+        <v>106.0594478014935</v>
+      </c>
+      <c r="P16" s="5">
+        <v>10937</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D17" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3">
+        <v>50</v>
+      </c>
+      <c r="G17" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1.08748963496342</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.4080952240111893</v>
+      </c>
+      <c r="J17" s="4">
+        <v>2.042365877984765</v>
+      </c>
+      <c r="K17" s="4">
+        <v>53.92176870748298</v>
+      </c>
+      <c r="L17" s="4">
+        <v>56.63832960477158</v>
+      </c>
+      <c r="M17" s="5">
+        <v>30</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1761323.483705521</v>
+      </c>
+      <c r="O17" s="4">
+        <v>105.1976039960294</v>
+      </c>
+      <c r="P17" s="5">
+        <v>16743</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,16 +5320,16 @@
         <v>8</v>
       </c>
       <c r="K3" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="M3" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N3" s="5">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3253,13 +5367,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3294,16 +5408,16 @@
         <v>8</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3341,13 +5455,13 @@
         <v>1</v>
       </c>
       <c r="L6" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -3470,16 +5584,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3517,13 +5631,13 @@
         <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3558,16 +5672,16 @@
         <v>3</v>
       </c>
       <c r="K11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" s="5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3602,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3646,16 +5760,16 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3737,13 +5851,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
       </c>
       <c r="N15" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -3822,16 +5936,16 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3847,9 +5961,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>28</v>
+      </c>
+      <c r="E3" s="5">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>8</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>16</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>24</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>23</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>18</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>28</v>
+      </c>
+      <c r="E5" s="5">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5" s="5">
+        <v>8</v>
+      </c>
+      <c r="J5" s="5">
+        <v>8</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>14</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>24</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>23</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5">
+        <v>22</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>18</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>18</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>12</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>21</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>21</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5">
+        <v>23</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5">
+        <v>21</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>21</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>4</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>22</v>
+      </c>
+      <c r="E11" s="5">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5">
+        <v>13</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5">
+        <v>8</v>
+      </c>
+      <c r="I11" s="5">
+        <v>5</v>
+      </c>
+      <c r="J11" s="5">
+        <v>3</v>
+      </c>
+      <c r="K11" s="5">
+        <v>1</v>
+      </c>
+      <c r="L11" s="5">
+        <v>13</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>24</v>
+      </c>
+      <c r="E12" s="5">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>5</v>
+      </c>
+      <c r="I12" s="5">
+        <v>5</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>18</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>26</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5">
+        <v>20</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5">
+        <v>5</v>
+      </c>
+      <c r="I13" s="5">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>19</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5">
+        <v>20</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>20</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>16</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>21</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>17</v>
+      </c>
+      <c r="G15" s="5">
+        <v>3</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>8</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>19</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>19</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>17</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>9</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>20</v>
+      </c>
+      <c r="E17" s="5">
+        <v>3</v>
+      </c>
+      <c r="F17" s="5">
+        <v>15</v>
+      </c>
+      <c r="G17" s="5">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5">
+        <v>3</v>
+      </c>
+      <c r="I17" s="5">
+        <v>3</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <v>12</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6729,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6771,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,92 +6802,138 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.150458292397821</v>
+        <v>1.428235646667594</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.1013966863463907</v>
       </c>
       <c r="D3" s="4">
-        <v>1.272747234734857</v>
+        <v>0.8366534994395579</v>
       </c>
       <c r="E3" s="4">
-        <v>21.46938775510203</v>
+        <v>23.67006802721088</v>
       </c>
       <c r="F3" s="4">
-        <v>31.05816554809863</v>
+        <v>36.49664429530202</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.428235646667594</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1013966863463907</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.428235646667594</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1013966863463907</v>
-      </c>
+        <v>1.150458292397821</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.8366534994395579</v>
+        <v>1.272747234734857</v>
       </c>
       <c r="E4" s="4">
-        <v>23.67006802721088</v>
+        <v>21.46938775510203</v>
       </c>
       <c r="F4" s="4">
-        <v>36.49664429530202</v>
+        <v>31.05816554809863</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.150458292397821</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.052207508609482</v>
@@ -4042,9 +6971,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.052207508609482</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3395341471532447</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7000,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7019,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7061,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,92 +7092,138 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.655890906052235</v>
+        <v>0.4412440371956166</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.6486556947265569</v>
       </c>
       <c r="D3" s="4">
-        <v>1.755190349547843</v>
+        <v>0.3980567463185992</v>
       </c>
       <c r="E3" s="4">
-        <v>34.33333333333341</v>
+        <v>42.8095238095238</v>
       </c>
       <c r="F3" s="4">
-        <v>44.30536912751675</v>
+        <v>53.35570469798657</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>9</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4412440371956166</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6486556947265569</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4412440371956166</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6486556947265569</v>
-      </c>
+        <v>1.655890906052235</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.3980567463185992</v>
+        <v>1.755190349547843</v>
       </c>
       <c r="E4" s="4">
-        <v>42.8095238095238</v>
+        <v>34.33333333333341</v>
       </c>
       <c r="F4" s="4">
-        <v>53.35570469798657</v>
+        <v>44.30536912751675</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>9</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.655890906052235</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.9611956547794165</v>
@@ -4255,9 +7261,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9611956547794165</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7392715084835757</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7290,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7309,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7351,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,40 +7382,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.508585167849344</v>
+        <v>0.8235788638177042</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.128948850881244</v>
       </c>
       <c r="D3" s="4">
-        <v>1.211117606038135</v>
+        <v>0.5853047067293744</v>
       </c>
       <c r="E3" s="4">
-        <v>29.07823129251692</v>
+        <v>31.734693877551</v>
       </c>
       <c r="F3" s="4">
-        <v>34.50559284116313</v>
+        <v>42.4384787472035</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
         <v>7</v>
@@ -4386,40 +7441,54 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8235788638177042</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.128948850881244</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8235788638177042</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.128948850881244</v>
-      </c>
+        <v>1.508585167849344</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.5853047067293744</v>
+        <v>1.211117606038135</v>
       </c>
       <c r="E4" s="4">
-        <v>31.734693877551</v>
+        <v>29.07823129251692</v>
       </c>
       <c r="F4" s="4">
-        <v>42.4384787472035</v>
+        <v>34.50559284116313</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
         <v>7</v>
@@ -4427,10 +7496,24 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.508585167849344</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.668677722129692</v>
@@ -4468,9 +7551,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.668677722129692</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3520926254060157</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7580,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7599,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7641,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,92 +7672,142 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.305502646285032</v>
+        <v>0.8095176182593888</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7189681392584077</v>
+        <v>0.2646742229687504</v>
       </c>
       <c r="D3" s="4">
-        <v>0.856695588400379</v>
+        <v>0.4183075743056463</v>
       </c>
       <c r="E3" s="4">
-        <v>21.45578231292517</v>
+        <v>24.07823129251701</v>
       </c>
       <c r="F3" s="4">
-        <v>27.18008948545861</v>
+        <v>32.39597315436242</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>8</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8095176182593888</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2646742229687504</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8095176182593888</v>
+        <v>1.305502646285032</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2646742229687504</v>
+        <v>0.7189681392584077</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4183075743056463</v>
+        <v>0.856695588400379</v>
       </c>
       <c r="E4" s="4">
-        <v>24.07823129251701</v>
+        <v>21.45578231292517</v>
       </c>
       <c r="F4" s="4">
-        <v>32.39597315436242</v>
+        <v>27.18008948545861</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.305502646285032</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7189681392584077</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.289284212031728</v>
@@ -4681,9 +7845,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.289284212031728</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.202563802198469</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7874,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7893,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +7935,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,92 +7966,144 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8487651725964327</v>
+        <v>0.7322439478190745</v>
       </c>
       <c r="C3" s="4">
-        <v>1.223460316432683</v>
+        <v>0.7853716536320633</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8587006856081473</v>
+        <v>0.5729293086567224</v>
       </c>
       <c r="E3" s="4">
-        <v>56.98299319727892</v>
+        <v>57.44897959183673</v>
       </c>
       <c r="F3" s="4">
-        <v>56.70469798657708</v>
+        <v>63.89821029082783</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.7853716536320633</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7109363535757826</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5835544841781325</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7322439478190745</v>
+        <v>0.8487651725964327</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7853716536320633</v>
+        <v>1.223460316432683</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5729293086567224</v>
+        <v>0.8587006856081473</v>
       </c>
       <c r="E4" s="4">
-        <v>57.44897959183673</v>
+        <v>56.98299319727892</v>
       </c>
       <c r="F4" s="4">
-        <v>63.89821029082783</v>
+        <v>56.70469798657708</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8487651725964327</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.223460316432683</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6288790590292905</v>
@@ -4894,9 +8141,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6288790590292905</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.9365225107641398</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8170,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.136651778138612</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.428706260045295</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.384502860059946</v>
-      </c>
-      <c r="E3" s="4">
-        <v>33.79591836734694</v>
-      </c>
-      <c r="F3" s="4">
-        <v>33.76510067114094</v>
-      </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>7</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>7</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.431127466988059</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.15571395946091</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.9744743876134768</v>
-      </c>
-      <c r="E4" s="4">
-        <v>37.89795918367347</v>
-      </c>
-      <c r="F4" s="4">
-        <v>42.96644295302013</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>8</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>7</v>
-      </c>
-      <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.07398340108341</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1.516096138072527</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.9721605009441336</v>
-      </c>
-      <c r="E5" s="4">
-        <v>33.62244897959184</v>
-      </c>
-      <c r="F5" s="4">
-        <v>39.13422818791946</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>8</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>7</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.8368043941586848</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.8235127788458101</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.9718017620175715</v>
-      </c>
-      <c r="E3" s="4">
-        <v>32.18367346938775</v>
-      </c>
-      <c r="F3" s="4">
-        <v>38.64541387024607</v>
-      </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>8</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>8</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.44593740967847</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1268916547332708</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4733729682949047</v>
-      </c>
-      <c r="E4" s="4">
-        <v>31.15646258503401</v>
-      </c>
-      <c r="F4" s="4">
-        <v>37.10850111856831</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>7</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>7</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.225407485429676</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7718361505773998</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.8779370976000933</v>
-      </c>
-      <c r="E5" s="4">
-        <v>34.23809523809511</v>
-      </c>
-      <c r="F5" s="4">
-        <v>41.08948545861255</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>8</v>
-      </c>
-      <c r="K5" s="5">
-        <v>2</v>
-      </c>
-      <c r="L5" s="5">
-        <v>6</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/ZhaoImproved2019.xlsx
+++ b/public/downloads/ZhaoImproved2019.xlsx
@@ -2145,16 +2145,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04838457539003503</v>
+        <v>-0.03495645555074267</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2371043843460234</v>
+        <v>0.2334673235106972</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1513063049841898</v>
+        <v>0.1480288066250512</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -2204,16 +2204,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.148383240401354</v>
+        <v>0.06401325193256291</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5738148273977693</v>
+        <v>0.5706955950232798</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4842293499061472</v>
+        <v>0.3845097402175366</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.03787092604290828</v>
+        <v>-0.008544090974196727</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -4659,13 +4659,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.7295268617338352</v>
+        <v>0.743461063806231</v>
       </c>
       <c r="I7" s="4">
-        <v>0.854338263861921</v>
+        <v>0.835337079217745</v>
       </c>
       <c r="J7" s="4">
-        <v>0.7157839879399226</v>
+        <v>0.7436523920847141</v>
       </c>
       <c r="K7" s="4">
         <v>57.17460317460286</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4720225404209129</v>
+        <v>0.4697704426843076</v>
       </c>
       <c r="I10" s="4">
-        <v>0.233083390682943</v>
+        <v>0.2041089164075528</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2142124607509016</v>
+        <v>0.1928077819565679</v>
       </c>
       <c r="K10" s="4">
         <v>71.13832199546474</v>
@@ -8026,16 +8026,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7853716536320633</v>
+        <v>0.9943846847179998</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7109363535757826</v>
+        <v>0.7527389597929698</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5835544841781325</v>
+        <v>0.5417518779609451</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
